--- a/Result/profitability/2360.xlsx
+++ b/Result/profitability/2360.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.12</v>
       </c>
       <c r="M2" t="n">
-        <v>5.6025</v>
+        <v>6.695</v>
       </c>
       <c r="N2" t="n">
-        <v>56.6575</v>
+        <v>56.88125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.2</v>
       </c>
       <c r="M3" t="n">
-        <v>5.328749999999999</v>
+        <v>6.4075</v>
       </c>
       <c r="N3" t="n">
-        <v>52.29625</v>
+        <v>52.3925</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.08</v>
       </c>
       <c r="M4" t="n">
-        <v>5.02625</v>
+        <v>5.913749999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>48.03749999999999</v>
+        <v>48.04625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.06</v>
       </c>
       <c r="M5" t="n">
-        <v>4.404999999999999</v>
+        <v>5.342499999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>43.05375</v>
+        <v>42.43624999999999</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.25</v>
       </c>
       <c r="M6" t="n">
-        <v>3.8575</v>
+        <v>3.875</v>
       </c>
       <c r="N6" t="n">
-        <v>37.57125000000001</v>
+        <v>37.655</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.49</v>
       </c>
       <c r="M7" t="n">
-        <v>2.419999999999999</v>
+        <v>3.18125</v>
       </c>
       <c r="N7" t="n">
-        <v>32.83374999999999</v>
+        <v>32.79625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.79</v>
       </c>
       <c r="M8" t="n">
-        <v>1.76375</v>
+        <v>2.14</v>
       </c>
       <c r="N8" t="n">
-        <v>28.175</v>
+        <v>27.9125</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>13529</v>
+      </c>
+      <c r="D75" t="n">
+        <v>5344</v>
+      </c>
+      <c r="E75" t="n">
+        <v>8185</v>
+      </c>
+      <c r="F75" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="G75" t="n">
+        <v>5241</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>38.74%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1272</v>
+      </c>
+      <c r="J75" t="n">
+        <v>6514</v>
+      </c>
+      <c r="K75" t="n">
+        <v>5123</v>
+      </c>
+      <c r="L75" t="n">
+        <v>12.13</v>
+      </c>
+      <c r="M75" t="n">
+        <v>6.97875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>61.005</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>3.010000000000002</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3300438596491231</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.100000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.0335463258785943</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>7.500000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.619870410367171</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-4.939999999999998</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.07548899755501215</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
